--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/SourceSheetWithWhitespace/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/SourceSheetWithWhitespace/outputfile.xlsx
@@ -405,66 +405,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="B2">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
